--- a/data/trans_orig/P23_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>293262</t>
+          <t>292564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345841</t>
+          <t>347821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139780</t>
+          <t>140079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184711</t>
+          <t>184670</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>447718</t>
+          <t>447062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>517184</t>
+          <t>516602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348171</t>
+          <t>346191</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400750</t>
+          <t>401448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>503640</t>
+          <t>503681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>548571</t>
+          <t>548272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>865179</t>
+          <t>865761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>934645</t>
+          <t>935301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>375494</t>
+          <t>373616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>437488</t>
+          <t>439900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198837</t>
+          <t>200682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253178</t>
+          <t>254330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>594892</t>
+          <t>594392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>679527</t>
+          <t>677643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>523270</t>
+          <t>520858</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585264</t>
+          <t>587142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>715215</t>
+          <t>714063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>769556</t>
+          <t>767711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1249624</t>
+          <t>1251508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1334259</t>
+          <t>1334759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230192</t>
+          <t>229328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>280930</t>
+          <t>281630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148437</t>
+          <t>150497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192863</t>
+          <t>195841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>388591</t>
+          <t>391018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459894</t>
+          <t>459703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>397579</t>
+          <t>396879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448317</t>
+          <t>449181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>490978</t>
+          <t>488000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535404</t>
+          <t>533344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902456</t>
+          <t>902647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>973759</t>
+          <t>971332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>378493</t>
+          <t>375409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>438036</t>
+          <t>433560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>276166</t>
+          <t>276920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>333702</t>
+          <t>336028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>665141</t>
+          <t>668781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>752175</t>
+          <t>754773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504186</t>
+          <t>508662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>563729</t>
+          <t>566813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704910</t>
+          <t>702584</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762446</t>
+          <t>761692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1228659</t>
+          <t>1226061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1315693</t>
+          <t>1312053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1325414</t>
+          <t>1329366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1442511</t>
+          <t>1446641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>814610</t>
+          <t>815961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>918767</t>
+          <t>910974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2170312</t>
+          <t>2166858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2328069</t>
+          <t>2330261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1832990</t>
+          <t>1828860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1950087</t>
+          <t>1946135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2460430</t>
+          <t>2468223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2564587</t>
+          <t>2563236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4326629</t>
+          <t>4324437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4484386</t>
+          <t>4487840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243855</t>
+          <t>241666</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297606</t>
+          <t>297842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138243</t>
+          <t>139879</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185378</t>
+          <t>186263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>397080</t>
+          <t>396699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>469908</t>
+          <t>467375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405863</t>
+          <t>405627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459614</t>
+          <t>461803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>511672</t>
+          <t>510787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>558807</t>
+          <t>557171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>930611</t>
+          <t>933144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1003439</t>
+          <t>1003820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>372168</t>
+          <t>372841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>438059</t>
+          <t>439126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>261603</t>
+          <t>259776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>320443</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>652558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>739020</t>
+          <t>743528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,29%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578859</t>
+          <t>577792</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>644750</t>
+          <t>644077</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>711741</t>
+          <t>710641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>770581</t>
+          <t>772408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1310082</t>
+          <t>1305574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1398769</t>
+          <t>1396544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285721</t>
+          <t>287218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>344951</t>
+          <t>342561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205264</t>
+          <t>202796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>260365</t>
+          <t>254893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502775</t>
+          <t>502382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>584218</t>
+          <t>582649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>415062</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471902</t>
+          <t>470405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515813</t>
+          <t>521285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570914</t>
+          <t>573382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>949583</t>
+          <t>951152</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031026</t>
+          <t>1031419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,25%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>335214</t>
+          <t>336096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397767</t>
+          <t>397070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>265440</t>
+          <t>263906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>324672</t>
+          <t>324290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>616867</t>
+          <t>618317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>703414</t>
+          <t>703259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549972</t>
+          <t>550669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>612525</t>
+          <t>611643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>726243</t>
+          <t>726625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>785475</t>
+          <t>787009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1295240</t>
+          <t>1295395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1381787</t>
+          <t>1380337</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1296941</t>
+          <t>1297780</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1415781</t>
+          <t>1415261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>920492</t>
+          <t>921956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1029014</t>
+          <t>1029669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2245409</t>
+          <t>2252453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2417827</t>
+          <t>2413925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2009968</t>
+          <t>2010488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2128808</t>
+          <t>2127969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2527313</t>
+          <t>2526658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2635835</t>
+          <t>2634371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4564249</t>
+          <t>4568151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4736667</t>
+          <t>4729623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225737</t>
+          <t>226604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273338</t>
+          <t>274142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>147594</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192436</t>
+          <t>193579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385481</t>
+          <t>381436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>457496</t>
+          <t>454408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401462</t>
+          <t>400658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449063</t>
+          <t>448196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>479294</t>
+          <t>478151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>524136</t>
+          <t>523748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>889034</t>
+          <t>892122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>961049</t>
+          <t>965094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311167</t>
+          <t>308944</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>370782</t>
+          <t>371510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>243123</t>
+          <t>244246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302717</t>
+          <t>300278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>565869</t>
+          <t>567400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>652277</t>
+          <t>651704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>650577</t>
+          <t>649849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>710192</t>
+          <t>712415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>739268</t>
+          <t>741707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>798862</t>
+          <t>797739</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1411067</t>
+          <t>1411640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1497475</t>
+          <t>1495944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>285451</t>
+          <t>281510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342623</t>
+          <t>338439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197755</t>
+          <t>202924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252480</t>
+          <t>254572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>499962</t>
+          <t>500489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>575888</t>
+          <t>580755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>416065</t>
+          <t>420249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473237</t>
+          <t>477178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530415</t>
+          <t>528323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>585140</t>
+          <t>579971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965694</t>
+          <t>960827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1041620</t>
+          <t>1041093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>258200</t>
+          <t>262270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>317739</t>
+          <t>319350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>230990</t>
+          <t>229682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288153</t>
+          <t>286428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>504909</t>
+          <t>503823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>583757</t>
+          <t>584957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>619828</t>
+          <t>618217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>679367</t>
+          <t>675297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>754341</t>
+          <t>756066</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>811504</t>
+          <t>812812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1396304</t>
+          <t>1395104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1475152</t>
+          <t>1476238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1133536</t>
+          <t>1132509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1249039</t>
+          <t>1247052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>873361</t>
+          <t>871670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>978159</t>
+          <t>977404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2029989</t>
+          <t>2032585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2191972</t>
+          <t>2190225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2143375</t>
+          <t>2145362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2258878</t>
+          <t>2259905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2560944</t>
+          <t>2561699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2665742</t>
+          <t>2667433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4739545</t>
+          <t>4741292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4901528</t>
+          <t>4898932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>292564</t>
+          <t>294085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>347821</t>
+          <t>347706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140079</t>
+          <t>141926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184670</t>
+          <t>184318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>447062</t>
+          <t>444332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>516602</t>
+          <t>516970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346191</t>
+          <t>346306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401448</t>
+          <t>399927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>503681</t>
+          <t>504033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>548272</t>
+          <t>546425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>865761</t>
+          <t>865393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>935301</t>
+          <t>938031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>373616</t>
+          <t>371898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439900</t>
+          <t>435767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200682</t>
+          <t>198869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254330</t>
+          <t>250804</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>594392</t>
+          <t>590162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>677643</t>
+          <t>675784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>520858</t>
+          <t>524991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587142</t>
+          <t>588860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>714063</t>
+          <t>717589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>767711</t>
+          <t>769524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1251508</t>
+          <t>1253367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1334759</t>
+          <t>1338989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229328</t>
+          <t>227819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>281630</t>
+          <t>280555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150497</t>
+          <t>150521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195841</t>
+          <t>195218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391018</t>
+          <t>389477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459703</t>
+          <t>457456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>396879</t>
+          <t>397954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>449181</t>
+          <t>450690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488000</t>
+          <t>488623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533344</t>
+          <t>533320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902647</t>
+          <t>904894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>971332</t>
+          <t>972873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>375409</t>
+          <t>375854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>433560</t>
+          <t>435213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>276920</t>
+          <t>274234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>336028</t>
+          <t>334530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>668781</t>
+          <t>670828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>754773</t>
+          <t>752181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>508662</t>
+          <t>507009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566813</t>
+          <t>566368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702584</t>
+          <t>704082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761692</t>
+          <t>764378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1226061</t>
+          <t>1228653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1312053</t>
+          <t>1310006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1329366</t>
+          <t>1331274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1446641</t>
+          <t>1442553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>815961</t>
+          <t>815438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>910974</t>
+          <t>919173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2166858</t>
+          <t>2173732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2330261</t>
+          <t>2325182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1828860</t>
+          <t>1832948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1946135</t>
+          <t>1944227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2468223</t>
+          <t>2460024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2563236</t>
+          <t>2563759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4324437</t>
+          <t>4329516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4487840</t>
+          <t>4480966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241666</t>
+          <t>245260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297842</t>
+          <t>298644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139879</t>
+          <t>139050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186263</t>
+          <t>187463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>396699</t>
+          <t>393956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>467375</t>
+          <t>465300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405627</t>
+          <t>404825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461803</t>
+          <t>458209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>510787</t>
+          <t>509587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>557171</t>
+          <t>558000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>933144</t>
+          <t>935219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1003820</t>
+          <t>1006563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>372841</t>
+          <t>374223</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439126</t>
+          <t>441099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>259776</t>
+          <t>261558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>321543</t>
+          <t>324483</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>652558</t>
+          <t>652427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>743528</t>
+          <t>741023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577792</t>
+          <t>575819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>644077</t>
+          <t>642695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>710641</t>
+          <t>707701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>772408</t>
+          <t>770626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1305574</t>
+          <t>1308079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1396544</t>
+          <t>1396675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,16%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>287218</t>
+          <t>286103</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>342561</t>
+          <t>340681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202796</t>
+          <t>204801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254893</t>
+          <t>261056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502382</t>
+          <t>507170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>582649</t>
+          <t>585346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>415062</t>
+          <t>416942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470405</t>
+          <t>471520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521285</t>
+          <t>515122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573382</t>
+          <t>571377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>951152</t>
+          <t>948455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031419</t>
+          <t>1026631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>336096</t>
+          <t>335213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397070</t>
+          <t>397455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263906</t>
+          <t>262785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>324290</t>
+          <t>322803</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>618317</t>
+          <t>614330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>703259</t>
+          <t>700019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>550669</t>
+          <t>550284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611643</t>
+          <t>612526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>726625</t>
+          <t>728112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>787009</t>
+          <t>788130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1295395</t>
+          <t>1298635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1380337</t>
+          <t>1384324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1297780</t>
+          <t>1296778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1415261</t>
+          <t>1414730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>921956</t>
+          <t>920335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1029669</t>
+          <t>1033648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2252453</t>
+          <t>2253291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2413925</t>
+          <t>2411864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2010488</t>
+          <t>2011019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2127969</t>
+          <t>2128971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2526658</t>
+          <t>2522679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2634371</t>
+          <t>2635992</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4568151</t>
+          <t>4570212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4729623</t>
+          <t>4728785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226604</t>
+          <t>224999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274142</t>
+          <t>275259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>147590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193579</t>
+          <t>192771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381436</t>
+          <t>383405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>454408</t>
+          <t>454703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400658</t>
+          <t>399541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448196</t>
+          <t>449801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>478151</t>
+          <t>478959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>523748</t>
+          <t>524140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>892122</t>
+          <t>891827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>965094</t>
+          <t>963125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>308944</t>
+          <t>310393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371510</t>
+          <t>370178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244246</t>
+          <t>241982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300278</t>
+          <t>300105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>567400</t>
+          <t>569169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>651704</t>
+          <t>650692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>649849</t>
+          <t>651181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>712415</t>
+          <t>710966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>741707</t>
+          <t>741880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>797739</t>
+          <t>800003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1411640</t>
+          <t>1412652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1495944</t>
+          <t>1494175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>281510</t>
+          <t>285142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338439</t>
+          <t>341422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202924</t>
+          <t>201681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254572</t>
+          <t>252364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>500489</t>
+          <t>502215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>580755</t>
+          <t>579090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420249</t>
+          <t>417266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477178</t>
+          <t>473546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>528323</t>
+          <t>530531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579971</t>
+          <t>581214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>960827</t>
+          <t>962492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1041093</t>
+          <t>1039367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>262270</t>
+          <t>260180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>319350</t>
+          <t>316492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>230295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>286428</t>
+          <t>284468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>503823</t>
+          <t>504002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>584957</t>
+          <t>583241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618217</t>
+          <t>621075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>675297</t>
+          <t>677387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>756066</t>
+          <t>758026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>812812</t>
+          <t>812199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395104</t>
+          <t>1396820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1476238</t>
+          <t>1476059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1132509</t>
+          <t>1141425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1247052</t>
+          <t>1252088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>871670</t>
+          <t>871656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>977404</t>
+          <t>984620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2032585</t>
+          <t>2034452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2190225</t>
+          <t>2193205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2145362</t>
+          <t>2140326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2259905</t>
+          <t>2250989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2561699</t>
+          <t>2554483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2667433</t>
+          <t>2667447</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4741292</t>
+          <t>4738312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4898932</t>
+          <t>4897065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
